--- a/assets/templates/Truman_Homes_Mileage_Report_TEMPLATE.xlsx
+++ b/assets/templates/Truman_Homes_Mileage_Report_TEMPLATE.xlsx
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="G1" s="143" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" s="78">
